--- a/artfynd/A 29857-2020 artfynd.xlsx
+++ b/artfynd/A 29857-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117979193</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 29857-2020 artfynd.xlsx
+++ b/artfynd/A 29857-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126633144</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58087</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nyhygget , Finsta Ängar Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>551098</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6685040</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Dag Lanerfeldt</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Dag Lanerfeldt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
